--- a/data/trans_camb/P13_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,5</t>
+          <t>-1,5; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,74</t>
+          <t>-3,64; -0,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,15</t>
+          <t>-3,52; -0,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,73</t>
+          <t>-2,8; 1,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,8</t>
+          <t>-2,96; 0,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,66</t>
+          <t>-3,7; -0,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,34</t>
+          <t>-1,28; 1,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,35</t>
+          <t>-2,5; -0,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -0,92</t>
+          <t>-2,93; -0,74</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 237,09</t>
+          <t>-53,76; 219,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,79</t>
+          <t>-100,0; -2,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,87</t>
+          <t>-100,0; 119,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,5; 105,7</t>
+          <t>-73,81; 95,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,16; 73,62</t>
+          <t>-79,49; 79,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3,98</t>
+          <t>-100,0; 7,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 90,09</t>
+          <t>-45,18; 103,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,88; -8,67</t>
+          <t>-85,96; -10,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-99,03; -30,28</t>
+          <t>-99,13; -34,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,61</t>
+          <t>-0,33; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,11</t>
+          <t>-0,76; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,87</t>
+          <t>0,52; 5,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,83</t>
+          <t>-0,33; 3,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,91</t>
+          <t>-2,42; 0,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,74</t>
+          <t>-1,55; 2,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,63</t>
+          <t>0,2; 2,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,05</t>
+          <t>-1,04; 1,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,42</t>
+          <t>0,17; 3,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 343,76</t>
+          <t>-24,62; 356,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 290,72</t>
+          <t>-48,36; 304,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 723,27</t>
+          <t>13,77; 809,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 247,43</t>
+          <t>-14,85; 223,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 87,32</t>
+          <t>-74,48; 60,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,21; 170,23</t>
+          <t>-51,1; 169,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 197,63</t>
+          <t>5,28; 203,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 82,91</t>
+          <t>-48,54; 84,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 253,03</t>
+          <t>-2,38; 244,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,42</t>
+          <t>-2,48; 2,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,53</t>
+          <t>-2,91; 1,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,79</t>
+          <t>-2,75; 1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,95</t>
+          <t>1,16; 5,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,42</t>
+          <t>-2,34; 1,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,53</t>
+          <t>-1,97; 1,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,35</t>
+          <t>0,2; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,08</t>
+          <t>-1,95; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,14</t>
+          <t>-1,92; 1,18</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 84,11</t>
+          <t>-46,66; 75,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 58,18</t>
+          <t>-56,3; 59,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 65,01</t>
+          <t>-54,01; 60,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,99; 261,03</t>
+          <t>25,35; 250,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 69,06</t>
+          <t>-54,09; 60,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 71,27</t>
+          <t>-48,52; 66,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 118,72</t>
+          <t>1,96; 123,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 38,01</t>
+          <t>-43,9; 34,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 43,59</t>
+          <t>-42,42; 43,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,04</t>
+          <t>0,85; 5,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,8</t>
+          <t>0,78; 4,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,03</t>
+          <t>-0,55; 4,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,44</t>
+          <t>1,55; 7,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,11</t>
+          <t>-0,41; 4,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,71</t>
+          <t>-1,87; 2,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,37</t>
+          <t>1,78; 5,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,17</t>
+          <t>0,84; 4,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,69</t>
+          <t>-1,02; 2,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 601,53</t>
+          <t>21,47; 713,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,97; 634,88</t>
+          <t>5,43; 622,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 442,26</t>
+          <t>-22,18; 539,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,86; 258,22</t>
+          <t>25,98; 277,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 169,52</t>
+          <t>-8,54; 178,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 94,85</t>
+          <t>-33,54; 96,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,9; 251,64</t>
+          <t>47,44; 262,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,17; 206,6</t>
+          <t>21,07; 205,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 127,09</t>
+          <t>-23,96; 131,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,6</t>
+          <t>-1,93; 3,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,53</t>
+          <t>-1,6; 3,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,86</t>
+          <t>0,68; 5,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,99</t>
+          <t>0,98; 8,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,34</t>
+          <t>-1,45; 5,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,6</t>
+          <t>-0,25; 5,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,98</t>
+          <t>0,38; 4,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,62</t>
+          <t>-0,69; 3,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,93</t>
+          <t>1,33; 5,02</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 182,08</t>
+          <t>-43,9; 169,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,26; 200,17</t>
+          <t>-40,36; 200,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,35; 299,47</t>
+          <t>7,01; 266,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,82; 222,45</t>
+          <t>11,76; 213,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 136,12</t>
+          <t>-20,03; 146,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 161,36</t>
+          <t>-5,9; 144,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,61; 155,35</t>
+          <t>6,92; 149,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 112,08</t>
+          <t>-14,23; 105,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,09; 156,95</t>
+          <t>22,8; 151,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 6,16</t>
+          <t>-2,0; 6,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,42</t>
+          <t>-5,92; 1,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 4,41</t>
+          <t>-3,04; 4,22</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,65; 12,51</t>
+          <t>2,92; 12,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 1,61</t>
+          <t>-6,15; 1,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 0,81</t>
+          <t>-8,29; 1,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,36</t>
+          <t>1,65; 8,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,16</t>
+          <t>-4,96; 0,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,24</t>
+          <t>-5,42; 1,45</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 150,82</t>
+          <t>-26,13; 162,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,71; 43,19</t>
+          <t>-69,94; 31,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 117,44</t>
+          <t>-34,83; 100,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24,28; 200,84</t>
+          <t>25,39; 192,05</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 27,07</t>
+          <t>-58,02; 24,15</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 10,57</t>
+          <t>-73,64; 14,45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,08; 144,42</t>
+          <t>14,95; 131,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,76; 1,63</t>
+          <t>-56,42; 5,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,37; 17,9</t>
+          <t>-59,87; 21,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 9,92</t>
+          <t>-2,29; 9,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 3,98</t>
+          <t>-6,2; 4,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 8,95</t>
+          <t>-1,89; 8,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,43; 18,58</t>
+          <t>5,99; 18,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 8,21</t>
+          <t>-3,27; 8,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,78</t>
+          <t>6,71; 16,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,93</t>
+          <t>4,26; 13,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,05</t>
+          <t>-3,01; 4,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,67</t>
+          <t>5,04; 12,21</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 135,74</t>
+          <t>-20,0; 137,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 60,87</t>
+          <t>-48,8; 65,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 132,93</t>
+          <t>-13,69; 129,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38,96; 185,33</t>
+          <t>37,34; 181,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 76,86</t>
+          <t>-22,51; 84,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,74; 162,59</t>
+          <t>41,43; 172,57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,24; 137,51</t>
+          <t>32,22; 139,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 52,19</t>
+          <t>-21,76; 49,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>36,33; 135,0</t>
+          <t>32,94; 125,87</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,49</t>
+          <t>0,36; 2,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,08</t>
+          <t>-0,66; 1,21</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,75</t>
+          <t>0,48; 2,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,74</t>
+          <t>3,3; 5,8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,79</t>
+          <t>-0,33; 1,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,05</t>
+          <t>0,52; 3,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,72</t>
+          <t>2,28; 3,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,19</t>
+          <t>-0,23; 1,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,58</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,65; 87,05</t>
+          <t>9,0; 89,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 37,89</t>
+          <t>-18,14; 44,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12,19; 101,55</t>
+          <t>13,83; 94,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59,61; 133,82</t>
+          <t>60,4; 133,07</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 41,35</t>
+          <t>-5,9; 42,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,59; 70,61</t>
+          <t>9,97; 74,16</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,49; 99,88</t>
+          <t>51,46; 102,31</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 31,99</t>
+          <t>-5,34; 34,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>21,51; 71,03</t>
+          <t>21,36; 70,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P13_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,43</t>
+          <t>-1,52; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,64</t>
+          <t>-3,45; -0,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,24</t>
+          <t>-2,5; 1,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,54</t>
+          <t>-2,49; 1,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,96</t>
+          <t>-2,97; 0,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,6</t>
+          <t>-3,93; -0,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,62</t>
+          <t>-1,28; 1,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; -0,28</t>
+          <t>-2,55; -0,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,74</t>
+          <t>-2,59; 0,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-78,16%</t>
+          <t>-41,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-85,52%</t>
+          <t>-85,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-82,01%</t>
+          <t>-64,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 219,61</t>
+          <t>-55,11; 249,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,58</t>
+          <t>-100,0; -3,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,05</t>
+          <t>-100,0; 236,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,81; 95,5</t>
+          <t>-73,23; 106,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,49; 79,42</t>
+          <t>-80,49; 70,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,05</t>
+          <t>-100,0; -6,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 103,72</t>
+          <t>-45,11; 87,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,96; -10,67</t>
+          <t>-86,21; -8,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-99,13; -34,17</t>
+          <t>-93,0; 36,67</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>2,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,58</t>
+          <t>-0,25; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,9</t>
+          <t>-0,66; 2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,79</t>
+          <t>0,85; 6,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,61</t>
+          <t>-0,39; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,73</t>
+          <t>-2,45; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,63</t>
+          <t>-1,1; 3,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,65</t>
+          <t>0,16; 2,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,03</t>
+          <t>-1,1; 1,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,6</t>
+          <t>0,55; 3,87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220,06%</t>
+          <t>251,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>114,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 356,5</t>
+          <t>-26,04; 318,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 304,2</t>
+          <t>-47,34; 260,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 809,04</t>
+          <t>34,94; 750,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 223,5</t>
+          <t>-13,35; 253,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,48; 60,36</t>
+          <t>-74,91; 60,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 169,31</t>
+          <t>-36,39; 193,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 203,3</t>
+          <t>5,2; 201,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 84,25</t>
+          <t>-49,77; 81,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 244,75</t>
+          <t>18,39; 262,69</t>
         </is>
       </c>
     </row>
@@ -1066,37 +1066,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>-0,91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,36</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,21</t>
+          <t>-2,19; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,61</t>
+          <t>-3,13; 1,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,72</t>
+          <t>-3,53; 1,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,99</t>
+          <t>1,04; 5,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,44</t>
+          <t>-2,28; 1,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,45</t>
+          <t>-2,14; 1,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,65</t>
+          <t>0,15; 3,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,91</t>
+          <t>-1,93; 1,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,18</t>
+          <t>-1,98; 0,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,72%</t>
+          <t>-22,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-9,54%</t>
+          <t>-10,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-16,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 75,17</t>
+          <t>-41,0; 79,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 59,19</t>
+          <t>-58,14; 45,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 60,37</t>
+          <t>-62,87; 38,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,35; 250,94</t>
+          <t>23,39; 269,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 60,12</t>
+          <t>-56,01; 62,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 66,35</t>
+          <t>-49,76; 69,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 123,9</t>
+          <t>3,44; 123,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 34,13</t>
+          <t>-45,46; 36,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 43,09</t>
+          <t>-45,82; 25,7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,03</t>
+          <t>0,87; 5,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,9</t>
+          <t>0,9; 4,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,19</t>
+          <t>1,01; 5,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,47</t>
+          <t>1,46; 7,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,91</t>
+          <t>-0,11; 5,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,59</t>
+          <t>-1,44; 2,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,5</t>
+          <t>1,8; 5,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,19</t>
+          <t>0,79; 4,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,65</t>
+          <t>0,39; 3,61</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124,21%</t>
+          <t>202,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>70,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,47; 713,49</t>
+          <t>18,5; 604,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 622,97</t>
+          <t>27,89; 592,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 539,83</t>
+          <t>23,22; 617,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,98; 277,38</t>
+          <t>26,91; 268,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 178,98</t>
+          <t>-4,03; 189,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 96,33</t>
+          <t>-25,78; 107,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,44; 262,19</t>
+          <t>48,39; 268,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,07; 205,46</t>
+          <t>22,21; 200,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 131,03</t>
+          <t>5,94; 178,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,57</t>
+          <t>-1,54; 3,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,39</t>
+          <t>-1,69; 3,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,81</t>
+          <t>0,53; 5,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,23</t>
+          <t>0,84; 8,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,21</t>
+          <t>-1,15; 5,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,43</t>
+          <t>-0,02; 5,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,82</t>
+          <t>0,35; 4,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,52</t>
+          <t>-0,85; 3,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,02</t>
+          <t>1,06; 4,97</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 169,37</t>
+          <t>-35,0; 182,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 200,71</t>
+          <t>-38,94; 159,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,01; 266,37</t>
+          <t>7,78; 279,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,76; 213,06</t>
+          <t>9,15; 215,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 146,04</t>
+          <t>-17,63; 144,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 144,42</t>
+          <t>-2,31; 162,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,92; 149,91</t>
+          <t>5,79; 146,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 105,9</t>
+          <t>-17,96; 104,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,8; 151,3</t>
+          <t>16,88; 158,41</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>0,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,78</t>
+          <t>-2,53; 6,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 1,19</t>
+          <t>-5,8; 1,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,22</t>
+          <t>-3,14; 3,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,81</t>
+          <t>2,53; 12,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 1,49</t>
+          <t>-6,43; 1,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,04</t>
+          <t>-3,21; 3,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,24</t>
+          <t>1,77; 8,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,32</t>
+          <t>-4,89; 0,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,45</t>
+          <t>-2,02; 2,98</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-35,03%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-18,06%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 162,85</t>
+          <t>-33,8; 145,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 31,46</t>
+          <t>-69,05; 34,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 100,93</t>
+          <t>-37,02; 89,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25,39; 192,05</t>
+          <t>23,13; 183,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 24,15</t>
+          <t>-59,73; 19,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,64; 14,45</t>
+          <t>-30,24; 54,98</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,95; 131,55</t>
+          <t>21,18; 139,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 5,98</t>
+          <t>-55,72; 7,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-59,87; 21,0</t>
+          <t>-23,01; 50,47</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,88</t>
+          <t>8,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 9,91</t>
+          <t>-2,55; 9,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 4,19</t>
+          <t>-6,81; 4,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,78</t>
+          <t>-1,78; 8,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,99; 18,07</t>
+          <t>6,54; 18,88</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 8,67</t>
+          <t>-3,48; 8,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,71; 16,57</t>
+          <t>6,83; 16,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,28</t>
+          <t>4,42; 13,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,89</t>
+          <t>-2,66; 5,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,21</t>
+          <t>4,8; 11,83</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 137,75</t>
+          <t>-21,21; 132,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 65,23</t>
+          <t>-50,1; 66,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 129,42</t>
+          <t>-13,72; 129,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37,34; 181,68</t>
+          <t>37,88; 183,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 84,96</t>
+          <t>-23,27; 79,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,43; 172,57</t>
+          <t>39,86; 171,04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,22; 139,25</t>
+          <t>31,26; 138,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 49,72</t>
+          <t>-19,29; 53,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>32,94; 125,87</t>
+          <t>33,43; 122,31</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>2,34</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,5</t>
+          <t>0,6; 2,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,21</t>
+          <t>-0,61; 1,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,69</t>
+          <t>1,09; 3,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,8</t>
+          <t>3,3; 5,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,81</t>
+          <t>-0,52; 1,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,21</t>
+          <t>1,58; 3,66</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,8</t>
+          <t>2,16; 3,81</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,27</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>1,66; 3,02</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>9,0; 89,38</t>
+          <t>15,65; 97,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 44,29</t>
+          <t>-17,34; 40,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13,83; 94,27</t>
+          <t>29,4; 112,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>60,4; 133,07</t>
+          <t>60,87; 133,53</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 42,1</t>
+          <t>-9,66; 39,7</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,97; 74,16</t>
+          <t>28,17; 87,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,46; 102,31</t>
+          <t>50,02; 104,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 34,72</t>
+          <t>-4,3; 33,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>21,36; 70,38</t>
+          <t>38,17; 83,38</t>
         </is>
       </c>
     </row>
